--- a/Field-trails/Pig-Slurry 2025-11-05/DFC overview pig.xlsx
+++ b/Field-trails/Pig-Slurry 2025-11-05/DFC overview pig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Fall-field-trails\Pig-Slurry 2025-11-05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\Pig-Slurry 2025-11-05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08432A96-FC12-4ADB-B6F9-51425D91C0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00DA8F7-FD18-4B4F-844E-EEF499DD54A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>Notes</t>
   </si>
@@ -139,6 +139,24 @@
   </si>
   <si>
     <t>Water opserved dripping from DFC 8</t>
+  </si>
+  <si>
+    <t>Q [L/s]</t>
+  </si>
+  <si>
+    <t>Const</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>[-]</t>
+  </si>
+  <si>
+    <t>emperical correction factor</t>
   </si>
 </sst>
 </file>
@@ -475,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.109375" bestFit="1" customWidth="1"/>
@@ -484,7 +502,7 @@
     <col min="7" max="7" width="20.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>45966</v>
       </c>
@@ -503,8 +521,20 @@
       <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -523,8 +553,21 @@
       <c r="G2" s="4">
         <v>0.49166666666666664</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <f>(F2^0.5)*$J$2</f>
+        <v>34.571664698131038</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -543,8 +586,12 @@
       <c r="G3" s="4">
         <v>0.49166666666666664</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <f t="shared" ref="H3:H20" si="0">(F3^0.5)*$J$2</f>
+        <v>33.285131815872383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -563,8 +610,12 @@
       <c r="G4" s="4">
         <v>0.49166666666666697</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>33.217465285599381</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -583,8 +634,12 @@
       <c r="G5" s="4">
         <v>0.50138888888888888</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>33.231009614515173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -603,8 +658,12 @@
       <c r="G6" s="4">
         <v>0.50138888888888888</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>33.231009614515173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>6</v>
       </c>
@@ -620,8 +679,12 @@
       <c r="G7" s="4">
         <v>0.50138888888888899</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>33.608034753612117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -640,8 +703,12 @@
       <c r="G8" s="4">
         <v>0.50138888888888899</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>34.047026301866659</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>8</v>
       </c>
@@ -657,8 +724,12 @@
       <c r="G9" s="4">
         <v>7.7083333333333337E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>33.79497003993346</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -677,8 +748,12 @@
       <c r="G10" s="4">
         <v>7.7083333333333337E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>33.79497003993346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -697,8 +772,12 @@
       <c r="G11" s="4">
         <v>8.4722222222222227E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>34.126236241343697</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>11</v>
       </c>
@@ -714,8 +793,12 @@
       <c r="G12" s="4">
         <v>9.0277777777777776E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>33.054500450014373</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -734,8 +817,12 @@
       <c r="G13" s="4">
         <v>9.5138888888888884E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>33.446972957204963</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -754,8 +841,12 @@
       <c r="G14" s="4">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>33.541019662496851</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>14</v>
       </c>
@@ -771,8 +862,12 @@
       <c r="G15" s="4">
         <v>0.10555555555555556</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>33.741665637605976</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -791,8 +886,12 @@
       <c r="G16" s="4">
         <v>0.1111111111111111</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>35.887323667278395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -811,8 +910,12 @@
       <c r="G17" s="4">
         <v>0.1111111111111111</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>35.887323667278395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>17</v>
       </c>
@@ -828,8 +931,12 @@
       <c r="G18" s="4">
         <v>0.12222222222222222</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>34.895558456628834</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -848,8 +955,12 @@
       <c r="G19" s="4">
         <v>0.12777777777777777</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>33.460424384636852</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -867,6 +978,10 @@
       </c>
       <c r="G20" s="4">
         <v>0.133333333333333</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>34.113047357279591</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/Pig-Slurry 2025-11-05/DFC overview pig.xlsx
+++ b/Field-trails/Pig-Slurry 2025-11-05/DFC overview pig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\Pig-Slurry 2025-11-05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00DA8F7-FD18-4B4F-844E-EEF499DD54A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999721EB-CC28-4CD8-9604-A76F428A2C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,9 +88,6 @@
     <t>H2SO4</t>
   </si>
   <si>
-    <t>No acid</t>
-  </si>
-  <si>
     <t>AA</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>emperical correction factor</t>
+  </si>
+  <si>
+    <t>RAW</t>
   </si>
 </sst>
 </file>
@@ -519,19 +519,19 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>27</v>
-      </c>
-      <c r="L1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -561,10 +561,10 @@
         <v>3</v>
       </c>
       <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -617,7 +617,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -755,7 +755,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -764,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>129.4</v>
@@ -785,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12">
         <v>121.4</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13">
         <v>124.3</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14">
         <v>13</v>
@@ -854,7 +854,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>126.5</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -878,7 +878,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>143.1</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>16</v>
@@ -923,7 +923,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18">
         <v>135.30000000000001</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>18</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20">
         <v>19</v>
